--- a/data.mn/public/datasets/mongolbank-exchange-rates-daily.xlsx
+++ b/data.mn/public/datasets/mongolbank-exchange-rates-daily.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exchange Rates (EN)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exchange Rates (MN)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Exchange Rates (EN)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Exchange Rates (MN)" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,6 +416,17 @@
   </sheetPr>
   <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -494,7 +505,7 @@
         <v>493.26</v>
       </c>
       <c r="I2" t="n">
-        <v>513.03</v>
+        <v>523.24</v>
       </c>
     </row>
     <row r="3">
@@ -527,7 +538,7 @@
         <v>4008.91</v>
       </c>
       <c r="I3" t="n">
-        <v>4198.52</v>
+        <v>4156.77</v>
       </c>
     </row>
     <row r="4">
@@ -560,7 +571,7 @@
         <v>23.72</v>
       </c>
       <c r="I4" t="n">
-        <v>22.85</v>
+        <v>22.53</v>
       </c>
     </row>
     <row r="5">
@@ -593,7 +604,7 @@
         <v>2.5</v>
       </c>
       <c r="I5" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="6">
@@ -626,7 +637,7 @@
         <v>42.64</v>
       </c>
       <c r="I6" t="n">
-        <v>45.98</v>
+        <v>46.07</v>
       </c>
     </row>
     <row r="7">
@@ -659,7 +670,7 @@
         <v>3545.29</v>
       </c>
       <c r="I7" t="n">
-        <v>3563.02</v>
+        <v>3575.62</v>
       </c>
     </row>
   </sheetData>
@@ -675,6 +686,17 @@
   </sheetPr>
   <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -753,7 +775,7 @@
         <v>493.26</v>
       </c>
       <c r="I2" t="n">
-        <v>513.03</v>
+        <v>523.24</v>
       </c>
     </row>
     <row r="3">
@@ -786,7 +808,7 @@
         <v>4008.91</v>
       </c>
       <c r="I3" t="n">
-        <v>4198.52</v>
+        <v>4156.77</v>
       </c>
     </row>
     <row r="4">
@@ -819,7 +841,7 @@
         <v>23.72</v>
       </c>
       <c r="I4" t="n">
-        <v>22.85</v>
+        <v>22.53</v>
       </c>
     </row>
     <row r="5">
@@ -852,7 +874,7 @@
         <v>2.5</v>
       </c>
       <c r="I5" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="6">
@@ -885,7 +907,7 @@
         <v>42.64</v>
       </c>
       <c r="I6" t="n">
-        <v>45.98</v>
+        <v>46.07</v>
       </c>
     </row>
     <row r="7">
@@ -918,7 +940,7 @@
         <v>3545.29</v>
       </c>
       <c r="I7" t="n">
-        <v>3563.02</v>
+        <v>3575.62</v>
       </c>
     </row>
   </sheetData>
